--- a/artfynd/A 30666-2023 artfynd.xlsx
+++ b/artfynd/A 30666-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30666-2023 artfynd.xlsx
+++ b/artfynd/A 30666-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90903817</v>
+        <v>125022971</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +708,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väst Ösjön, Vg</t>
+          <t>Ösjön, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>359747.9526525228</v>
+        <v>359712</v>
       </c>
       <c r="R2" t="n">
-        <v>6393225.819164672</v>
+        <v>6393152</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,15 +786,121 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Per-Anders Nilsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Per-Anders Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>90903817</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Väst Ösjön, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>359748</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6393226</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Sara Elg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Sara Elg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30666-2023 artfynd.xlsx
+++ b/artfynd/A 30666-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125022971</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,8 +911,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>